--- a/output/2026-09-08_03_Croazia_Krapinsko-zagorska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-08_03_Croazia_Krapinsko-zagorska_ATEX_Equipment-Services.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
